--- a/AAII_Financials/Quarterly/GFL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>GFL</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1371600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1177600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1229900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1216300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1228300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1085400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1092000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1150400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1155600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1057400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1425700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1397200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1467800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1329700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1821200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1831200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1707500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1401400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1539500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1381300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1216100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1099600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1235600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1036000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>993300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>931300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>896500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>898000</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1092500</v>
+      </c>
+      <c r="E9" s="3">
         <v>956300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>979000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>948400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>953800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>884300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>887200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>929300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>941800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>878400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1190900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1125900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1197200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1145400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1624200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1591900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1482000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1265600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1431600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1204500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1104400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1008800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1363000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>909500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>881300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>852300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>859300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>797200</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>279100</v>
+      </c>
+      <c r="E10" s="3">
         <v>221400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>251000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>267900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>274500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>201100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>204700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>221200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>213800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>179000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>234700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>271300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>270600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>184300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>197000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>239300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>225500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>135800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>107900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>176800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>111700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>90800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-127400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>126500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>112000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>79000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>37200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>100800</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,79 +1259,82 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E14" s="3">
         <v>11000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-45600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-110600</v>
       </c>
-      <c r="G14" s="3">
-        <v>-11400</v>
-      </c>
       <c r="H14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I14" s="3">
         <v>18000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-17200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>372800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>18600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-412800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-5300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-6500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-135700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-31400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>13800</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>21400</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1322,100 +1342,106 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>41800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>284500</v>
+      </c>
+      <c r="E15" s="3">
         <v>240900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>202800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>249100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>246700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>230600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>191200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>304200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>298500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>275300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>219600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>264700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>287300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>285500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>7900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>7700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>7600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>7200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>6500</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>5900</v>
       </c>
       <c r="AB15" s="3">
         <v>5900</v>
       </c>
       <c r="AC15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AD15" s="3">
         <v>5500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1277000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1139700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1151600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1088800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1110700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1068700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1061500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1071200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1084900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1049200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1399900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1282900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1351700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1295000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1820700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1784400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1669500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1421800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1465800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1318200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1247600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1135600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1529200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1013900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>985400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1007400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1014300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>899000</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>94600</v>
+      </c>
+      <c r="E18" s="3">
         <v>38000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>78300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>127500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>117600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>79200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>70700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>114300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>116100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>34700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>38000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-20400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>73700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>63100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-31500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-293600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>22100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-76100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-117800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,248 +1680,255 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E20" s="3">
         <v>137000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>51600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-167400</v>
-      </c>
       <c r="H20" s="3">
-        <v>70100</v>
+        <v>-171100</v>
       </c>
       <c r="I20" s="3">
+        <v>81900</v>
+      </c>
+      <c r="J20" s="3">
         <v>192600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-79900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>84200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-39100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>108300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-114700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-183800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>91600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>223600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-68600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-331000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>145700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-201000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-383100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-181700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-161700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-289600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>271400</v>
+      </c>
+      <c r="E21" s="3">
         <v>141800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>285400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>324900</v>
       </c>
-      <c r="G21" s="3">
-        <v>531700</v>
-      </c>
       <c r="H21" s="3">
-        <v>177200</v>
+        <v>535400</v>
       </c>
       <c r="I21" s="3">
+        <v>165400</v>
+      </c>
+      <c r="J21" s="3">
         <v>29100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>463300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>352800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>199300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>284500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>368500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>388800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>211900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>291200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>248200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>501700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>558200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>370600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>68300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>436000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>77600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-129500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>74300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>80900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-143900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>119500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E22" s="3">
         <v>83000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>98100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>76600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>72300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>97500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>97200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>107400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>106600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>98000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>103900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>86000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>109000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>99600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>135500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>122500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>94900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>88000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>96000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>87700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>81900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>80300</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
@@ -1899,186 +1939,195 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>123900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-129600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-195000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>107500</v>
       </c>
-      <c r="G23" s="3">
-        <v>221600</v>
-      </c>
       <c r="H23" s="3">
-        <v>-185300</v>
+        <v>207400</v>
       </c>
       <c r="I23" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-246000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>42300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-430400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-175800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-61300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>402300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-192100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-249700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-259500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>34700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>115200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-90900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-355600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>32300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-317300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-676700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-153800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-365700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-253100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-143200</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-38000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-22900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>29900</v>
       </c>
-      <c r="G24" s="3">
-        <v>20500</v>
-      </c>
       <c r="H24" s="3">
-        <v>-36500</v>
+        <v>17000</v>
       </c>
       <c r="I24" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="J24" s="3">
         <v>-99100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-41700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-31200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-14300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-13300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>180400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-30600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-75800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-47900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-21800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>69700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-39500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-22200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-33600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-82500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-44900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-38300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-87700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-72800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-33300</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-114500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-157000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>53000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>77600</v>
       </c>
-      <c r="G26" s="3">
-        <v>201000</v>
-      </c>
       <c r="H26" s="3">
-        <v>-148800</v>
+        <v>190400</v>
       </c>
       <c r="I26" s="3">
+        <v>-157700</v>
+      </c>
+      <c r="J26" s="3">
         <v>-146900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-388600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-144600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-47000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>221900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-219100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-183700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>82600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>137000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-160600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-316100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>54500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-283700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-594200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-114700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-115500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-278000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-180300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-120600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-162600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>73600</v>
       </c>
-      <c r="G27" s="3">
-        <v>193900</v>
-      </c>
       <c r="H27" s="3">
-        <v>2361800</v>
+        <v>183200</v>
       </c>
       <c r="I27" s="3">
+        <v>2352900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-141200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>66600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-360600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-145000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-58000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>205600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-178900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-220000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-183500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>82600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>137000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-160600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-316100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>54500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-283700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-594200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-114700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-115500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-278000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-180300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2430,32 +2491,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-35400</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>2519100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>8300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>51100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>43500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>14300</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2472,29 +2533,29 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-18300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-109600</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>6200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>8000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1700</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-107700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-137000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-51600</v>
       </c>
-      <c r="G32" s="3">
-        <v>167400</v>
-      </c>
       <c r="H32" s="3">
-        <v>-70100</v>
+        <v>171100</v>
       </c>
       <c r="I32" s="3">
+        <v>-81900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-192600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>79900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-84200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>39100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-108300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>114700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>183800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-91600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-223600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>68600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>331000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-145700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>201000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>383100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>181700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>161700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>289600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>11400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-112500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-154500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>82100</v>
       </c>
-      <c r="G33" s="3">
-        <v>202600</v>
-      </c>
       <c r="H33" s="3">
-        <v>2372100</v>
+        <v>192000</v>
       </c>
       <c r="I33" s="3">
+        <v>2363300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-131400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-344300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-127600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-39500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>222700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-162200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-220000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-183500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>64300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-160600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-309900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>62500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-282000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-594200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-114700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-115500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-278000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-180300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-112500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-154500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>82100</v>
       </c>
-      <c r="G35" s="3">
-        <v>202600</v>
-      </c>
       <c r="H35" s="3">
-        <v>2372100</v>
+        <v>192000</v>
       </c>
       <c r="I35" s="3">
+        <v>2363300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-131400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-344300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-127600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-39500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>222700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-162200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-220000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-183500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>64300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-160600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-309900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>62500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-282000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-594200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-114700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-115500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-278000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-180300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>135300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1028900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>62400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>139700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>102400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>373700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>93000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>73700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>98100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>102800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>128800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>62100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>82100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>237400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>230600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>189300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>190400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1149500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>310400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1817200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>723900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>91400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>574800</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,94 +3440,100 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>735900</v>
+      </c>
+      <c r="E43" s="3">
         <v>663300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>654900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>648400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>625400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>571700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>876500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>907100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>866500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>797800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>853900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>874400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>840700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>755100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1118100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1211500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1093600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>844600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1134700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1091200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>873900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>816100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>867300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>731500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>744000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>762000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>713400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>747800</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3480,8 +3576,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3522,19 +3618,22 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>44400</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -3542,11 +3641,11 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>74900</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
@@ -3554,204 +3653,210 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>74400</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>755100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>182900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>189000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>194800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>724900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>170600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>165600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>149300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>135600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>133700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>147200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>150600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>150400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>132100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>142500</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1022300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1802200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>849100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>978400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>879900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1118400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1178400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1188900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1176000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1036800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1124500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1186500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1092200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1713700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1383100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1637900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1519000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1758800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1495700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2406300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1333600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>962800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1028200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2695900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1618500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1003800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1420300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>890300</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1263100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1336400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1384300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1430400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1441800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1384100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>239400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>248300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>228600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>214500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>241600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>233700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>205300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>229300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>326600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>321600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>298000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>21300</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>8</v>
@@ -3765,8 +3870,8 @@
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3780,180 +3885,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5721000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5345100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5341800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5143000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5011400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4839400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5457000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5447100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5355800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5205200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5285900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5073600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4834400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4731000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6540300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6538800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6047100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5656200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6010600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5572000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5007100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5052300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5074800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3258600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3301300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3362800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2850100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2774400</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6955100</v>
+      </c>
+      <c r="E49" s="3">
         <v>6268300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6310100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6108800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6029700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5951000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7574900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7827200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7843600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8157800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8289100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8097900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7837500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7929800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11427400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11475500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11209400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10470300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10831100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10111100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9319200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9458200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9593800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8780900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8944400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9302600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8021800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8100600</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>198600</v>
+      </c>
+      <c r="E52" s="3">
         <v>198700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>187300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>235100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>221500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>254500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>144100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>80500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>83300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>92000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>83200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>44900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>52600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>90200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>40600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>38500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>35900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>36300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>35300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>35800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33800</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>33500</v>
       </c>
       <c r="AB52" s="3">
         <v>33500</v>
       </c>
       <c r="AC52" s="3">
+        <v>33500</v>
+      </c>
+      <c r="AD52" s="3">
         <v>31700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15160100</v>
+      </c>
+      <c r="E54" s="3">
         <v>14950600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14072600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13895700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13584300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13547300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14739200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14907000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14814200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14805500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15052800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14703700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14014300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14656400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19767600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20014400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19112000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17942500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18373700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18125600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15695200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15509100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15730000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>14769200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13897700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13702700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12323800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11796200</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,524 +4576,543 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1265500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1104800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>620500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1209300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1149600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1223200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>564600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1183500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1217900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1131900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>538400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1147900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1089300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1019900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1557700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1496000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1371900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1119000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1319700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1177400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>990800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>950000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1014800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>747500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>701500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>749500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>732000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>698200</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E58" s="3">
         <v>52900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>43700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>162600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>127100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>97500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>847100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>814600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>56800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>58300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>56900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>44100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>43000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>56600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>69400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>69500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>66800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>63900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>68100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>67900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>57300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>56800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>42100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>43300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>42600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>44700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>97500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E59" s="3">
         <v>35800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>253400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>39500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>196900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>199900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>106300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>280200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>68700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1065000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>981100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>962800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1260100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>134600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>137700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>140000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>141000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>136400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>109300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>97400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>98100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>35500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1358300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1193500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1457100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1411400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1320800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1360400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2189800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2041900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1322600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1233100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1370900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1298300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1412500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1145200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2692100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2546600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2401500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2443000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1522400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1383000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1188100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1147800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1193300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>900100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>841500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>892300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>865100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>820600</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7089500</v>
+      </c>
+      <c r="E61" s="3">
         <v>7034600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5742200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5490600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5159000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5108100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6484500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6600200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7347300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7042100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6976600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6815300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6219100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7306200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9576200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9695600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9061300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8285500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8219200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8647300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6716100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6345600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6315200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6201400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5235700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4647800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7719500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7006300</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>906700</v>
+      </c>
+      <c r="E62" s="3">
         <v>874400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>846800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>792100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>771900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>768000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>723000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>750300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>707600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>693400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>708100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>629500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>668600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>663700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1455200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1450600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1505000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1515500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2856000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2567400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2378700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2624100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2542200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2006200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1993700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2029600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>971300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>981100</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9849700</v>
+      </c>
+      <c r="E66" s="3">
         <v>9604900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8613300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8291500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7801100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7780800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9720100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9721600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9732200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9351200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9459900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9149700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8628900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9515500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13730400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13698800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12967800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12244000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12597600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12597700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10282900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10117500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10050700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9107700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8070900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7569700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9555900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8808000</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-153900</v>
+      </c>
+      <c r="E72" s="3">
         <v>4500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>167400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>145900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>70800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-119500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2483600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2499600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2542700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2216800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2137300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2043200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2099100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2267500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2843000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2617400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2428500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2487800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2510500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2237600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1988000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2008700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1778300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1163800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1048300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-770300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-590000</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5181800</v>
+      </c>
+      <c r="E76" s="3">
         <v>5215300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5326200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5464100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5617500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5599200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4850000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5017100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4927200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5298500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5434600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5388400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5374000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5128600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6037200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6315600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6144200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5698500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5776100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5527900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5412300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5391600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5679300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5661500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5826800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6133000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2767900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2988200</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-112500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-154500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>82100</v>
       </c>
-      <c r="G81" s="3">
-        <v>202600</v>
-      </c>
       <c r="H81" s="3">
-        <v>2372100</v>
+        <v>192000</v>
       </c>
       <c r="I81" s="3">
+        <v>2363300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-131400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-344300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-127600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-39500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>222700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-162200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-220000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-183500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>64300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-160600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-309900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>62500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-282000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-594200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-114700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-115500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-278000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-180300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,94 +6605,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>192200</v>
+      </c>
+      <c r="E83" s="3">
         <v>179400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>200200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>213900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>209900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>188300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>215400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>179100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>179600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>177200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>192300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>187200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>185600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>405400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>385200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>372100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>355000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>365500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>336200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>321800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>314600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>547200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>233900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>234700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>221800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>248700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>194300</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>293900</v>
+      </c>
+      <c r="E89" s="3">
         <v>120200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>324800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>280800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>224400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>120700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>392900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>256900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>266400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>194400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>303900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>93000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>196900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>142300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>403000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>286100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>231200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>176000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>283800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>223900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>177500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>212700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>163500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>256700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>173300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-91300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>133000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>81700</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-202500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-276700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-181100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-207800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-211900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-218900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-220500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-208100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-218000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-218800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-175300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-204300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-208900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-237300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-210600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-129000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-203200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-229400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-134700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-151800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-131300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-122600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-85700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-119800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-143800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-107100</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1139600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-373000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-420200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-297800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-316700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3743900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-218600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-229200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-486900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-290900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-385400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-471600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>995500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-356000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-404300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-334700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-804600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-190600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1136600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1133400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-221400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-195800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2893800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-105800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-128200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1225700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-236300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-551800</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7461,36 +7695,36 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-5600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-5400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-5000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-4700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-4800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-4500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1210700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>56900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-187500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3591600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-138700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-54600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>271500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>48000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>61000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>447200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1189400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>212000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-150500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>67700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>632200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>19600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1734600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>359500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-28700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>974100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>942100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>662500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>759600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>674600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E101" s="3">
         <v>7700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4100</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-13600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-17500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>14000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-16300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-33800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-75100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>74000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-876100</v>
+      </c>
+      <c r="E102" s="3">
         <v>967600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-79500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-291500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>280700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>23800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>46900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-29200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>68000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-155300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>41300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-959100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>839100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>299300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1790000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1093300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>632500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-483400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>574800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-209300</v>
       </c>
     </row>
